--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,887 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128681484</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>675052</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6564763</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128681483</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92782</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>674788</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6565036</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128676174</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>674599</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6564750</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar intill en tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128681476</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95929</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>675141</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6564732</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128681478</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>675053</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6565013</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128681477</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92740</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>675006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6564847</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128681474</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90967</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>675098</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6564749</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128681475</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90967</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>675140</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6564734</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128675840</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98579</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>674679</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6564816</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett flertal exemplar.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,6 +1195,16 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1202,7 +1212,7 @@
         <v>128681476</v>
       </c>
       <c r="B7" t="n">
-        <v>95929</v>
+        <v>95935</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1309,7 @@
         <v>128681478</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92740</v>
+        <v>92746</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>90967</v>
+        <v>90973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>90967</v>
+        <v>90973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1788,126 @@
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128693765</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>674843</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6564855</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1209,32 +1209,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128681476</v>
+        <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>95935</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675141</v>
+        <v>675053</v>
       </c>
       <c r="R7" t="n">
-        <v>6564732</v>
+        <v>6565013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,32 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128681478</v>
+        <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>92790</v>
+        <v>95935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675053</v>
+        <v>675141</v>
       </c>
       <c r="R8" t="n">
-        <v>6565013</v>
+        <v>6564732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1909,6 +1909,430 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128717747</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>674816</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6565145</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En fruktkropp.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128717859</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>674621</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6565026</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128717206</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>674650</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6564961</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128717695</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>674822</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6565133</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2333,6 +2333,1254 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128737780</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>674971</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6565154</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128736831</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91689</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rosetticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Postia floriformis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Quél.) Jülich</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>674864</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6565314</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128735669</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92790</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>674862</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6565270</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128735554</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91824</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>674855</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6565248</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128738613</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92790</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>674872</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6565202</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128735553</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>674855</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6565248</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128738703</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91426</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>674881</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6565245</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128735817</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>674894</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6565319</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128738796</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>674880</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6565242</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128736979</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>674876</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6565310</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128738401</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92752</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>674914</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6565161</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>92752</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,32 +3368,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3401,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R27" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3436,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3446,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3473,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B28" t="n">
-        <v>92752</v>
+        <v>4779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,26 +3478,32 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R28" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,6 +3580,663 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128770626</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>674960</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6564975</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128764851</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>674807</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6565024</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128761517</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>674829</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6565135</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128764468</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>674810</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6565023</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128764913</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92790</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>674797</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6565018</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128761569</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>674813</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6565121</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95937</v>
+        <v>95938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128717747</v>
       </c>
       <c r="B14" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128717859</v>
       </c>
       <c r="B15" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128717206</v>
       </c>
       <c r="B16" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>128717695</v>
       </c>
       <c r="B17" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,39 +2335,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128737780</v>
+        <v>128736831</v>
       </c>
       <c r="B18" t="n">
-        <v>92792</v>
+        <v>91690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>1100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Quél.) Jülich</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2377,13 +2373,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674971</v>
+        <v>674864</v>
       </c>
       <c r="R18" t="n">
-        <v>6565154</v>
+        <v>6565314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2412,7 +2408,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2422,7 +2418,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,6 +2427,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2449,35 +2446,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128736831</v>
+        <v>128737780</v>
       </c>
       <c r="B19" t="n">
-        <v>91689</v>
+        <v>92793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1100</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2487,13 +2488,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674864</v>
+        <v>674971</v>
       </c>
       <c r="R19" t="n">
-        <v>6565314</v>
+        <v>6565154</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,7 +2523,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2532,7 +2533,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2541,7 +2542,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>128735669</v>
       </c>
       <c r="B20" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>128735554</v>
       </c>
       <c r="B21" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>128738613</v>
       </c>
       <c r="B22" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>128735553</v>
       </c>
       <c r="B23" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128738703</v>
       </c>
       <c r="B24" t="n">
-        <v>91426</v>
+        <v>91427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>128735817</v>
       </c>
       <c r="B25" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B27" t="n">
-        <v>92752</v>
+        <v>4779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,26 +3368,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3395,13 +3401,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R27" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3430,7 +3436,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3446,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3473,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B28" t="n">
-        <v>4779</v>
+        <v>92753</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,32 +3484,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R28" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,7 +3586,7 @@
         <v>128770626</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128764851</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128764468</v>
       </c>
       <c r="B32" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>128764913</v>
       </c>
       <c r="B33" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128761569</v>
       </c>
       <c r="B34" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,6 +4238,220 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128804347</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>674637</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6564804</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gnagspår på en gran.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128804078</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92793</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>674640</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6565050</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett flertal fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95938</v>
+        <v>95965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128693765</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128717747</v>
       </c>
       <c r="B14" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128717859</v>
       </c>
       <c r="B15" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128717206</v>
       </c>
       <c r="B16" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>128717695</v>
       </c>
       <c r="B17" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>128736831</v>
       </c>
       <c r="B18" t="n">
-        <v>91690</v>
+        <v>91717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>128737780</v>
       </c>
       <c r="B19" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>128735669</v>
       </c>
       <c r="B20" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>128735554</v>
       </c>
       <c r="B21" t="n">
-        <v>91825</v>
+        <v>91852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>128738613</v>
       </c>
       <c r="B22" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>128735553</v>
       </c>
       <c r="B23" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128738703</v>
       </c>
       <c r="B24" t="n">
-        <v>91427</v>
+        <v>91454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>128735817</v>
       </c>
       <c r="B25" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>92780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,32 +3368,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3401,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R27" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3436,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3446,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3473,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B28" t="n">
-        <v>92753</v>
+        <v>4779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,26 +3478,32 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R28" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,7 +3586,7 @@
         <v>128770626</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128764851</v>
       </c>
       <c r="B30" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128764468</v>
       </c>
       <c r="B32" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>128764913</v>
       </c>
       <c r="B33" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128761569</v>
       </c>
       <c r="B34" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>128804078</v>
       </c>
       <c r="B36" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4452,6 +4452,2055 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128823598</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>674964</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6564964</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128822567</v>
+      </c>
+      <c r="B38" t="n">
+        <v>88708</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>805</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Scharlakansvaxing</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>674862</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6565255</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128829860</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>675057</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6564832</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackmärken på en tall.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128822764</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>674928</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6565117</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128829258</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>674968</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6564967</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128823232</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>674943</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6564963</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128823407</v>
+      </c>
+      <c r="B43" t="n">
+        <v>96108</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>674984</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6564992</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128822674</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>674928</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6565117</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128826779</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92056</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>674828</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6565119</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128824197</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92780</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>675083</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6564885</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128826613</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92820</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>674674</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6565110</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128829636</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>674968</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6564967</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128825464</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91003</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>675052</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6564838</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128826037</v>
+      </c>
+      <c r="B50" t="n">
+        <v>96108</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>674880</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6564888</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128825353</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92780</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>675052</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6564838</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128825694</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>308</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>675051</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6564828</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128822614</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>674862</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6565255</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128829154</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58575</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>674959</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6565013</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128826512</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91003</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>674674</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6565110</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128829056</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>674959</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6565131</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -2335,35 +2335,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736831</v>
+        <v>128737780</v>
       </c>
       <c r="B18" t="n">
-        <v>91717</v>
+        <v>92820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1100</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2373,13 +2377,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674864</v>
+        <v>674971</v>
       </c>
       <c r="R18" t="n">
-        <v>6565314</v>
+        <v>6565154</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2408,7 +2412,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2418,7 +2422,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,7 +2431,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2446,39 +2449,35 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128737780</v>
+        <v>128736831</v>
       </c>
       <c r="B19" t="n">
-        <v>92820</v>
+        <v>91717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>1100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Quél.) Jülich</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2488,13 +2487,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674971</v>
+        <v>674864</v>
       </c>
       <c r="R19" t="n">
-        <v>6565154</v>
+        <v>6565314</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2523,7 +2522,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2533,7 +2532,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,6 +2541,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -4773,48 +4773,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B40" t="n">
-        <v>92776</v>
+        <v>5177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R40" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,77 +4851,78 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B41" t="n">
-        <v>5177</v>
+        <v>92776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R41" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4948,30 +4954,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B49" t="n">
-        <v>91003</v>
+        <v>96108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,21 +5703,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5727,10 +5727,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R49" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5789,10 +5789,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B50" t="n">
-        <v>96108</v>
+        <v>91003</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R50" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,32 +5886,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B51" t="n">
-        <v>92780</v>
+        <v>75196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R51" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5983,32 +5983,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B52" t="n">
-        <v>75196</v>
+        <v>92780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R52" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95965</v>
+        <v>95971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128693765</v>
+        <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>91519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,35 +1813,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1849,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674843</v>
+        <v>674816</v>
       </c>
       <c r="R13" t="n">
-        <v>6564855</v>
+        <v>6565145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,12 +1870,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En fruktkropp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,6 +1889,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1911,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128717747</v>
+        <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>91514</v>
+        <v>92825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674816</v>
+        <v>674621</v>
       </c>
       <c r="R14" t="n">
-        <v>6565145</v>
+        <v>6565026</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,7 +1986,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>En fruktkropp.</t>
+          <t>Fyra fruktkroppar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128717859</v>
+        <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>92820</v>
+        <v>91519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674621</v>
+        <v>674650</v>
       </c>
       <c r="R15" t="n">
-        <v>6565026</v>
+        <v>6564961</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,7 +2092,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fyra fruktkroppar.</t>
+          <t>Två fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128717206</v>
+        <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674650</v>
+        <v>674822</v>
       </c>
       <c r="R16" t="n">
-        <v>6564961</v>
+        <v>6565133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,7 +2198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två fruktkroppar</t>
+          <t>En fruktkropp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2226,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128717695</v>
+        <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>91514</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,40 +2237,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674822</v>
+        <v>674971</v>
       </c>
       <c r="R17" t="n">
-        <v>6565133</v>
+        <v>6565154</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2297,17 +2298,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>En fruktkropp</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,58 +2322,53 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128737780</v>
+        <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2377,13 +2378,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674971</v>
+        <v>674862</v>
       </c>
       <c r="R18" t="n">
-        <v>6565154</v>
+        <v>6565270</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2412,7 +2413,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2422,7 +2423,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128736831</v>
+        <v>128735554</v>
       </c>
       <c r="B19" t="n">
-        <v>91717</v>
+        <v>91857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,25 +2461,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1100</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2487,13 +2492,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674864</v>
+        <v>674855</v>
       </c>
       <c r="R19" t="n">
-        <v>6565314</v>
+        <v>6565248</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2532,7 +2537,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2541,7 +2546,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2560,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128735669</v>
+        <v>128738613</v>
       </c>
       <c r="B20" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2589,7 +2593,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2598,13 +2606,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674862</v>
+        <v>674872</v>
       </c>
       <c r="R20" t="n">
-        <v>6565270</v>
+        <v>6565202</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2633,7 +2641,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2643,7 +2651,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,32 +2678,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735554</v>
+        <v>128735553</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>91499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,32 +2792,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738613</v>
+        <v>128735817</v>
       </c>
       <c r="B22" t="n">
-        <v>92818</v>
+        <v>91517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2826,13 +2834,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674872</v>
+        <v>674894</v>
       </c>
       <c r="R22" t="n">
-        <v>6565202</v>
+        <v>6565319</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2861,7 +2869,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2871,7 +2879,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,41 +2906,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735553</v>
+        <v>128738796</v>
       </c>
       <c r="B23" t="n">
-        <v>91494</v>
+        <v>4773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2940,13 +2950,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674855</v>
+        <v>674880</v>
       </c>
       <c r="R23" t="n">
-        <v>6565248</v>
+        <v>6565242</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2975,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2985,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,6 +3004,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3012,40 +3023,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738703</v>
+        <v>128738401</v>
       </c>
       <c r="B24" t="n">
-        <v>91454</v>
+        <v>92785</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5445</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3054,13 +3061,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674881</v>
+        <v>674914</v>
       </c>
       <c r="R24" t="n">
-        <v>6565245</v>
+        <v>6565161</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,7 +3096,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3106,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,41 +3133,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735817</v>
+        <v>128736979</v>
       </c>
       <c r="B25" t="n">
-        <v>91512</v>
+        <v>4779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3168,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674894</v>
+        <v>674876</v>
       </c>
       <c r="R25" t="n">
-        <v>6565319</v>
+        <v>6565310</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3203,7 +3212,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3213,7 +3222,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3240,57 +3249,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738796</v>
+        <v>128770626</v>
       </c>
       <c r="B26" t="n">
-        <v>4773</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674880</v>
+        <v>674960</v>
       </c>
       <c r="R26" t="n">
-        <v>6565242</v>
+        <v>6564975</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3314,22 +3314,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,55 +3328,58 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128738401</v>
+        <v>128764851</v>
       </c>
       <c r="B27" t="n">
-        <v>92780</v>
+        <v>91953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4363</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3395,13 +3388,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674914</v>
+        <v>674807</v>
       </c>
       <c r="R27" t="n">
-        <v>6565161</v>
+        <v>6565024</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3425,22 +3418,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128736979</v>
+        <v>128761517</v>
       </c>
       <c r="B28" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3504,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674876</v>
+        <v>674829</v>
       </c>
       <c r="R28" t="n">
-        <v>6565310</v>
+        <v>6565135</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
@@ -3541,22 +3534,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,48 +3576,51 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128770626</v>
+        <v>128764468</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>91499</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674960</v>
+        <v>674810</v>
       </c>
       <c r="R29" t="n">
-        <v>6564975</v>
+        <v>6565023</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3648,12 +3644,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3668,52 +3674,48 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128764851</v>
+        <v>128764913</v>
       </c>
       <c r="B30" t="n">
-        <v>91948</v>
+        <v>92823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3722,13 +3724,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674807</v>
+        <v>674797</v>
       </c>
       <c r="R30" t="n">
-        <v>6565024</v>
+        <v>6565018</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3757,7 +3759,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3767,7 +3769,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,43 +3796,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128761517</v>
+        <v>128761569</v>
       </c>
       <c r="B31" t="n">
-        <v>8439</v>
+        <v>92825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3838,13 +3834,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674829</v>
+        <v>674813</v>
       </c>
       <c r="R31" t="n">
-        <v>6565135</v>
+        <v>6565121</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3869,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3879,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,51 +3906,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128764468</v>
+        <v>128804347</v>
       </c>
       <c r="B32" t="n">
-        <v>91494</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674810</v>
+        <v>674637</v>
       </c>
       <c r="R32" t="n">
-        <v>6565023</v>
+        <v>6564804</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3978,22 +3976,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnagspår på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4002,50 +3995,51 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128764913</v>
+        <v>128804078</v>
       </c>
       <c r="B33" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4054,17 +4048,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674797</v>
+        <v>674640</v>
       </c>
       <c r="R33" t="n">
-        <v>6565018</v>
+        <v>6565050</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4088,22 +4082,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett flertal fruktkroppar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,28 +4101,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128761569</v>
+        <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>92820</v>
+        <v>88712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,40 +4131,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>805</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674813</v>
+        <v>674862</v>
       </c>
       <c r="R34" t="n">
-        <v>6565121</v>
+        <v>6565255</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4198,22 +4194,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4228,65 +4214,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128804347</v>
+        <v>128823598</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>674637</v>
+        <v>674964</v>
       </c>
       <c r="R35" t="n">
-        <v>6564804</v>
+        <v>6564964</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4310,17 +4296,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gnagspår på en gran.</t>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4329,29 +4315,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128804078</v>
+        <v>128829860</v>
       </c>
       <c r="B36" t="n">
-        <v>92820</v>
+        <v>57713</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,26 +4344,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4372,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674640</v>
+        <v>675057</v>
       </c>
       <c r="R36" t="n">
-        <v>6565050</v>
+        <v>6564832</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4416,17 +4402,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett flertal fruktkroppar.</t>
+          <t>Hackmärken på en tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,7 +4421,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4454,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128823598</v>
+        <v>128822764</v>
       </c>
       <c r="B37" t="n">
-        <v>57713</v>
+        <v>92781</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4465,39 +4450,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674964</v>
+        <v>674928</v>
       </c>
       <c r="R37" t="n">
-        <v>6564964</v>
+        <v>6565117</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4530,11 +4510,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4561,57 +4536,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128822567</v>
+        <v>128829258</v>
       </c>
       <c r="B38" t="n">
-        <v>88708</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>805</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674862</v>
+        <v>674968</v>
       </c>
       <c r="R38" t="n">
-        <v>6565255</v>
+        <v>6564967</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4643,76 +4614,78 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128829860</v>
+        <v>128823232</v>
       </c>
       <c r="B39" t="n">
-        <v>57713</v>
+        <v>92196</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>675057</v>
+        <v>674943</v>
       </c>
       <c r="R39" t="n">
-        <v>6564832</v>
+        <v>6564963</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4742,11 +4715,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackmärken på en tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4761,22 +4729,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128829258</v>
+        <v>128823407</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>96114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,42 +4752,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674968</v>
+        <v>674984</v>
       </c>
       <c r="R40" t="n">
-        <v>6564967</v>
+        <v>6564992</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4851,65 +4814,64 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128822764</v>
+        <v>128822674</v>
       </c>
       <c r="B41" t="n">
-        <v>92776</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
@@ -4978,10 +4940,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128823232</v>
+        <v>128826779</v>
       </c>
       <c r="B42" t="n">
-        <v>92191</v>
+        <v>92061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4989,37 +4951,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>3884</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674943</v>
+        <v>674828</v>
       </c>
       <c r="R42" t="n">
-        <v>6564963</v>
+        <v>6565119</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5043,12 +5008,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5057,28 +5022,44 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128823407</v>
+        <v>128824197</v>
       </c>
       <c r="B43" t="n">
-        <v>96108</v>
+        <v>92785</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5086,21 +5067,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2170</v>
+        <v>4363</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5110,10 +5091,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674984</v>
+        <v>675083</v>
       </c>
       <c r="R43" t="n">
-        <v>6564992</v>
+        <v>6564885</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5172,50 +5153,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128822674</v>
+        <v>128826613</v>
       </c>
       <c r="B44" t="n">
-        <v>4779</v>
+        <v>92825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674928</v>
+        <v>674674</v>
       </c>
       <c r="R44" t="n">
-        <v>6565117</v>
+        <v>6565110</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5274,10 +5250,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128826779</v>
+        <v>128829636</v>
       </c>
       <c r="B45" t="n">
-        <v>92056</v>
+        <v>5197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5285,26 +5261,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3884</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5312,13 +5290,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674828</v>
+        <v>674968</v>
       </c>
       <c r="R45" t="n">
-        <v>6565119</v>
+        <v>6564967</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5342,12 +5320,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5360,40 +5343,25 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>ekar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128824197</v>
+        <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>92780</v>
+        <v>96114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5369,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4363</v>
+        <v>2170</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675083</v>
+        <v>674880</v>
       </c>
       <c r="R46" t="n">
-        <v>6564885</v>
+        <v>6564888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5487,32 +5455,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128826613</v>
+        <v>128825464</v>
       </c>
       <c r="B47" t="n">
-        <v>92820</v>
+        <v>91008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5522,10 +5490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674674</v>
+        <v>675052</v>
       </c>
       <c r="R47" t="n">
-        <v>6565110</v>
+        <v>6564838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5584,53 +5552,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128829636</v>
+        <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>5197</v>
+        <v>75197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674968</v>
+        <v>675051</v>
       </c>
       <c r="R48" t="n">
-        <v>6564967</v>
+        <v>6564828</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5662,40 +5625,34 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128826037</v>
+        <v>128825353</v>
       </c>
       <c r="B49" t="n">
-        <v>96108</v>
+        <v>92785</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,21 +5660,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2170</v>
+        <v>4363</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5727,10 +5684,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R49" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5789,10 +5746,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128825464</v>
+        <v>128822614</v>
       </c>
       <c r="B50" t="n">
-        <v>91003</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,34 +5757,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5741</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>675052</v>
+        <v>674862</v>
       </c>
       <c r="R50" t="n">
-        <v>6564838</v>
+        <v>6565255</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,48 +5848,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128825694</v>
+        <v>128829154</v>
       </c>
       <c r="B51" t="n">
-        <v>75196</v>
+        <v>58575</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>208249</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>675051</v>
+        <v>674959</v>
       </c>
       <c r="R51" t="n">
-        <v>6564828</v>
+        <v>6565013</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5965,28 +5936,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128825353</v>
+        <v>128826512</v>
       </c>
       <c r="B52" t="n">
-        <v>92780</v>
+        <v>91008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5994,34 +5966,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4363</v>
+        <v>5741</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>675052</v>
+        <v>674674</v>
       </c>
       <c r="R52" t="n">
-        <v>6564838</v>
+        <v>6565110</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6080,7 +6061,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128822614</v>
+        <v>128829056</v>
       </c>
       <c r="B53" t="n">
         <v>5177</v>
@@ -6109,24 +6090,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674862</v>
+        <v>674959</v>
       </c>
       <c r="R53" t="n">
-        <v>6565255</v>
+        <v>6565131</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6158,81 +6139,81 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128829154</v>
+        <v>128736831</v>
       </c>
       <c r="B54" t="n">
-        <v>58575</v>
+        <v>91722</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>208249</v>
+        <v>1100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Quél.) Jülich</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674959</v>
+        <v>674864</v>
       </c>
       <c r="R54" t="n">
-        <v>6565013</v>
+        <v>6565314</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6256,12 +6237,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6277,229 +6268,15 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>128826512</v>
-      </c>
-      <c r="B55" t="n">
-        <v>91003</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>5741</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Tjockfotad fingersvamp</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Skansberget, Skansberget, Srm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>674674</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6565110</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Huddinge</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Huddinge</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>128829056</v>
-      </c>
-      <c r="B56" t="n">
-        <v>5177</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Vidja, Srm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>674959</v>
-      </c>
-      <c r="R56" t="n">
-        <v>6565131</v>
-      </c>
-      <c r="S56" t="n">
-        <v>25</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Huddinge</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Huddinge</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran.</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95971</v>
+        <v>95978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2450,32 +2450,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128735554</v>
+        <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>91857</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674855</v>
+        <v>674872</v>
       </c>
       <c r="R19" t="n">
-        <v>6565248</v>
+        <v>6565202</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2564,32 +2564,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738613</v>
+        <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674872</v>
+        <v>674855</v>
       </c>
       <c r="R20" t="n">
-        <v>6565202</v>
+        <v>6565248</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735553</v>
+        <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91499</v>
+        <v>91522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674855</v>
+        <v>674894</v>
       </c>
       <c r="R21" t="n">
-        <v>6565248</v>
+        <v>6565319</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2792,41 +2792,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128735817</v>
+        <v>128738796</v>
       </c>
       <c r="B22" t="n">
-        <v>91517</v>
+        <v>4773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2834,13 +2836,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674894</v>
+        <v>674880</v>
       </c>
       <c r="R22" t="n">
-        <v>6565319</v>
+        <v>6565242</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2869,7 +2871,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2879,7 +2881,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,6 +2890,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2906,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738796</v>
+        <v>128736979</v>
       </c>
       <c r="B23" t="n">
-        <v>4773</v>
+        <v>4779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,21 +2920,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2940,7 +2943,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2950,13 +2953,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674880</v>
+        <v>674876</v>
       </c>
       <c r="R23" t="n">
-        <v>6565242</v>
+        <v>6565310</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2985,7 +2988,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2998,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,7 +3007,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3026,7 +3028,7 @@
         <v>128738401</v>
       </c>
       <c r="B24" t="n">
-        <v>92785</v>
+        <v>92790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,57 +3135,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128736979</v>
+        <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>4779</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674876</v>
+        <v>674960</v>
       </c>
       <c r="R25" t="n">
-        <v>6565310</v>
+        <v>6564975</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3207,22 +3200,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3237,22 +3220,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128770626</v>
+        <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>91958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3260,37 +3243,44 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674960</v>
+        <v>674807</v>
       </c>
       <c r="R26" t="n">
-        <v>6564975</v>
+        <v>6565024</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3314,12 +3304,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3334,53 +3334,55 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128764851</v>
+        <v>128761517</v>
       </c>
       <c r="B27" t="n">
-        <v>91953</v>
+        <v>8439</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3388,13 +3390,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674807</v>
+        <v>674829</v>
       </c>
       <c r="R27" t="n">
-        <v>6565024</v>
+        <v>6565135</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3433,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,43 +3462,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128761517</v>
+        <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>8439</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3504,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674829</v>
+        <v>674810</v>
       </c>
       <c r="R28" t="n">
-        <v>6565135</v>
+        <v>6565023</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
@@ -3539,7 +3535,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3549,7 +3545,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3576,32 +3572,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128764468</v>
+        <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>91499</v>
+        <v>92830</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674810</v>
+        <v>674797</v>
       </c>
       <c r="R29" t="n">
-        <v>6565023</v>
+        <v>6565018</v>
       </c>
       <c r="S29" t="n">
         <v>6</v>
@@ -3649,7 +3645,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3655,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3682,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128764913</v>
+        <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92823</v>
+        <v>92832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3724,13 +3720,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674797</v>
+        <v>674813</v>
       </c>
       <c r="R30" t="n">
-        <v>6565018</v>
+        <v>6565121</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,7 +3755,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3769,7 +3765,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3796,51 +3792,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128761569</v>
+        <v>128804347</v>
       </c>
       <c r="B31" t="n">
-        <v>92825</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674813</v>
+        <v>674637</v>
       </c>
       <c r="R31" t="n">
-        <v>6565121</v>
+        <v>6564804</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3864,22 +3862,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gnagspår på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,57 +3881,56 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128804347</v>
+        <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>92832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3946,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674637</v>
+        <v>674640</v>
       </c>
       <c r="R32" t="n">
-        <v>6564804</v>
+        <v>6565050</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3986,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gnagspår på en gran.</t>
+          <t>Ett flertal fruktkroppar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4014,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128804078</v>
+        <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>92825</v>
+        <v>88713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,40 +4017,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>805</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674640</v>
+        <v>674862</v>
       </c>
       <c r="R33" t="n">
-        <v>6565050</v>
+        <v>6565255</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4082,17 +4080,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett flertal fruktkroppar.</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4101,29 +4094,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>88712</v>
+        <v>57713</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4131,31 +4123,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4164,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R34" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,6 +4188,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4219,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128823598</v>
+        <v>128829860</v>
       </c>
       <c r="B35" t="n">
         <v>57713</v>
@@ -4255,24 +4248,23 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>674964</v>
+        <v>675057</v>
       </c>
       <c r="R35" t="n">
-        <v>6564964</v>
+        <v>6564832</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,7 +4298,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hackmärken i död gran.</t>
+          <t>Hackmärken på en tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4321,22 +4313,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128829860</v>
+        <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>57713</v>
+        <v>92786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,41 +4336,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>675057</v>
+        <v>674928</v>
       </c>
       <c r="R36" t="n">
-        <v>6564832</v>
+        <v>6565117</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4408,11 +4396,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken på en tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,60 +4410,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B37" t="n">
-        <v>92781</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R37" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4512,34 +4500,40 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128829258</v>
+        <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>92201</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4547,42 +4541,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674968</v>
+        <v>674943</v>
       </c>
       <c r="R38" t="n">
-        <v>6564967</v>
+        <v>6564963</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4614,40 +4603,34 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128823232</v>
+        <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>92196</v>
+        <v>96121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4655,21 +4638,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4679,10 +4662,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674943</v>
+        <v>674984</v>
       </c>
       <c r="R39" t="n">
-        <v>6564963</v>
+        <v>6564992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,10 +4724,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B40" t="n">
-        <v>96114</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,34 +4735,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R40" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4838,10 +4826,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128822674</v>
+        <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>92066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,42 +4837,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>3884</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674928</v>
+        <v>674828</v>
       </c>
       <c r="R41" t="n">
-        <v>6565117</v>
+        <v>6565119</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4908,12 +4894,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4922,28 +4908,44 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128826779</v>
+        <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92061</v>
+        <v>92790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4951,40 +4953,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3884</v>
+        <v>4363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674828</v>
+        <v>675083</v>
       </c>
       <c r="R42" t="n">
-        <v>6565119</v>
+        <v>6564885</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5008,12 +5007,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,66 +5021,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>ekar</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128824197</v>
+        <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92785</v>
+        <v>92832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5091,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>675083</v>
+        <v>674674</v>
       </c>
       <c r="R43" t="n">
-        <v>6564885</v>
+        <v>6565110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5153,48 +5136,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826613</v>
+        <v>128829636</v>
       </c>
       <c r="B44" t="n">
-        <v>92825</v>
+        <v>5197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674674</v>
+        <v>674968</v>
       </c>
       <c r="R44" t="n">
-        <v>6565110</v>
+        <v>6564967</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5226,34 +5214,40 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128829636</v>
+        <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>5197</v>
+        <v>91013</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5261,42 +5255,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>5741</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674968</v>
+        <v>675052</v>
       </c>
       <c r="R45" t="n">
-        <v>6564967</v>
+        <v>6564838</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5328,30 +5317,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5361,7 +5344,7 @@
         <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>96114</v>
+        <v>96121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825464</v>
+        <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>91008</v>
+        <v>75197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5741</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R47" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5552,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>75197</v>
+        <v>92790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5587,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R48" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5649,10 +5632,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128825353</v>
+        <v>128822614</v>
       </c>
       <c r="B49" t="n">
-        <v>92785</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5660,34 +5643,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4363</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>675052</v>
+        <v>674862</v>
       </c>
       <c r="R49" t="n">
-        <v>6564838</v>
+        <v>6565255</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5746,10 +5734,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128822614</v>
+        <v>128829154</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>58575</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5757,42 +5745,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>208249</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674862</v>
+        <v>674959</v>
       </c>
       <c r="R50" t="n">
-        <v>6565255</v>
+        <v>6565013</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5830,28 +5822,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128829154</v>
+        <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>58575</v>
+        <v>91013</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,46 +5852,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>208249</v>
+        <v>5741</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674959</v>
+        <v>674674</v>
       </c>
       <c r="R51" t="n">
-        <v>6565013</v>
+        <v>6565110</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5936,29 +5929,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128826512</v>
+        <v>128829056</v>
       </c>
       <c r="B52" t="n">
-        <v>91008</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,46 +5958,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5741</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674674</v>
+        <v>674959</v>
       </c>
       <c r="R52" t="n">
-        <v>6565110</v>
+        <v>6565131</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6037,77 +6025,81 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128829056</v>
+        <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>5177</v>
+        <v>91727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>1100</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674959</v>
+        <v>674864</v>
       </c>
       <c r="R53" t="n">
-        <v>6565131</v>
+        <v>6565314</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6131,17 +6123,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran.</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6157,63 +6154,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128736831</v>
+        <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>91722</v>
+        <v>96878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1100</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674864</v>
+        <v>674836</v>
       </c>
       <c r="R54" t="n">
-        <v>6565314</v>
+        <v>6565193</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6237,22 +6231,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6261,22 +6255,759 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128897084</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92786</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>675050</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6565124</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Hanna Rönnols</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Hanna Rönnols</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128896962</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92806</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>675023</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6565128</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128894849</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>674836</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6565193</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128895773</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>674782</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6565036</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128896496</v>
+      </c>
+      <c r="B59" t="n">
+        <v>96074</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>210</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>674983</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6565095</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128896442</v>
+      </c>
+      <c r="B60" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>53</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>674963</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6565065</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128895670</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>674812</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6565025</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Hanna Rönnols</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Hanna Rönnols</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>4779</v>
+        <v>92790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,32 +2920,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R23" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B24" t="n">
-        <v>92790</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,26 +3030,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R24" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4325,48 +4325,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B36" t="n">
-        <v>92786</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R36" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4398,77 +4403,78 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>92786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R37" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4500,30 +4506,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>91013</v>
+        <v>96121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R45" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>96121</v>
+        <v>91013</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R46" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>75197</v>
+        <v>92790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R47" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>92790</v>
+        <v>75197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R48" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B57" t="n">
-        <v>91469</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R57" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R58" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7009,6 +7009,1178 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128918596</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>674844</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6565194</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128918598</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>674848</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6565258</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128918620</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92830</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>675101</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6564829</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128918593</v>
+      </c>
+      <c r="B65" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>674984</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6565057</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128918595</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>674863</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6565199</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128918619</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92830</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>674873</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6565272</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128918607</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91013</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>674610</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6564952</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128918597</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90536</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>674823</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6565098</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128918599</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>674811</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6565023</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128918608</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91013</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>674660</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6564999</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128918594</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>675018</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6564970</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128918621</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92133</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>674957</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6564925</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B23" t="n">
-        <v>92790</v>
+        <v>4779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,26 +2920,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2947,13 +2953,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R23" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,7 +2988,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2998,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B24" t="n">
-        <v>4779</v>
+        <v>92790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,32 +3036,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R24" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4325,53 +4325,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>92786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R36" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4403,78 +4398,77 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B37" t="n">
-        <v>92786</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R37" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4506,24 +4500,30 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95978</v>
+        <v>95982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>128738401</v>
       </c>
       <c r="B24" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>88713</v>
+        <v>88717</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>128829860</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92066</v>
+        <v>92070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>92790</v>
+        <v>75201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R47" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>75197</v>
+        <v>92794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R48" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
         <v>128829154</v>
       </c>
       <c r="B50" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91727</v>
+        <v>91731</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>91473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R57" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B58" t="n">
-        <v>91469</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R58" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96074</v>
+        <v>96078</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91469</v>
+        <v>91508</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R62" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91504</v>
+        <v>91473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R63" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92133</v>
+        <v>92137</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>4779</v>
+        <v>92794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,32 +2920,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R23" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,26 +3030,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R24" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B57" t="n">
-        <v>91473</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R57" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R58" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>96125</v>
+        <v>91017</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R45" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>91017</v>
+        <v>96125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R46" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B66" t="n">
-        <v>91473</v>
+        <v>92834</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R66" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B67" t="n">
-        <v>92834</v>
+        <v>91473</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R67" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95982</v>
+        <v>95989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B33" t="n">
-        <v>88717</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,31 +4017,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R33" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,6 +4082,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>57717</v>
+        <v>88722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,27 +4124,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R34" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,11 +4193,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4222,7 +4222,7 @@
         <v>128829860</v>
       </c>
       <c r="B35" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92070</v>
+        <v>92075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>128829154</v>
       </c>
       <c r="B50" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91731</v>
+        <v>91736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>91478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R57" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B58" t="n">
-        <v>91473</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R58" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96078</v>
+        <v>96085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>92834</v>
+        <v>91478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R66" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>91473</v>
+        <v>92839</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R67" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92137</v>
+        <v>92142</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95992</v>
+        <v>95997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91024</v>
+        <v>91029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91024</v>
+        <v>91029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>4779</v>
+        <v>92807</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,32 +2920,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R23" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B24" t="n">
-        <v>92807</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,26 +3030,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R24" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4325,48 +4325,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B36" t="n">
-        <v>92803</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R36" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4398,77 +4403,78 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>92803</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R37" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4500,30 +4506,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,39 +4638,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R39" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,10 +4724,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B40" t="n">
-        <v>96140</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4740,34 +4735,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R40" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>91029</v>
+        <v>96140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R45" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>96140</v>
+        <v>91029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R46" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B57" t="n">
-        <v>91485</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R57" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R58" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B66" t="n">
-        <v>91485</v>
+        <v>92847</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R66" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B67" t="n">
-        <v>92847</v>
+        <v>91485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R67" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B23" t="n">
-        <v>92807</v>
+        <v>4779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,26 +2920,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2947,13 +2953,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R23" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,7 +2988,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2998,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B24" t="n">
-        <v>4779</v>
+        <v>92812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,32 +3036,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R24" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3138,7 @@
         <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>88729</v>
+        <v>88732</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4325,53 +4325,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>92808</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R36" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4403,78 +4398,77 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B37" t="n">
-        <v>92803</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R37" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4506,24 +4500,30 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B39" t="n">
-        <v>96140</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,34 +4638,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R39" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4724,10 +4729,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>96145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4735,39 +4740,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R40" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92083</v>
+        <v>92088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>96140</v>
+        <v>91032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R45" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>91029</v>
+        <v>96145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R46" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5441,7 +5441,7 @@
         <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91743</v>
+        <v>91746</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>91488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R57" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B58" t="n">
-        <v>91485</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R58" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96093</v>
+        <v>96098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B62" t="n">
-        <v>91520</v>
+        <v>91488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R62" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B63" t="n">
-        <v>91485</v>
+        <v>91523</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R63" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>92847</v>
+        <v>91488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R66" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>91485</v>
+        <v>92852</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R67" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92150</v>
+        <v>92155</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>95997</v>
+        <v>96005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92803</v>
+        <v>92811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91029</v>
+        <v>91035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91029</v>
+        <v>91035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>4779</v>
+        <v>92815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,32 +2920,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R23" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B24" t="n">
-        <v>92812</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,26 +3030,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R24" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3138,7 @@
         <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>88732</v>
+        <v>88735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96148</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,39 +4638,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R39" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,10 +4724,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B40" t="n">
-        <v>96145</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4740,34 +4735,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R40" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92088</v>
+        <v>92091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92812</v>
+        <v>92815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>92812</v>
+        <v>92815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91746</v>
+        <v>91749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96098</v>
+        <v>96101</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91488</v>
+        <v>91526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R62" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91523</v>
+        <v>91491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R63" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B66" t="n">
-        <v>91488</v>
+        <v>92855</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R66" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B67" t="n">
-        <v>92852</v>
+        <v>91491</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R67" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7791,45 +7791,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B70" t="n">
-        <v>91523</v>
+        <v>91035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R70" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7870,6 +7873,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7888,48 +7892,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B71" t="n">
-        <v>91032</v>
+        <v>91526</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R71" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7970,7 +7971,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B33" t="n">
-        <v>88735</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,31 +4017,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R33" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,6 +4082,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>88735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,27 +4124,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R34" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,11 +4193,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>91035</v>
+        <v>96148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R45" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>96148</v>
+        <v>91035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R46" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>92855</v>
+        <v>91491</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R66" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>91491</v>
+        <v>92855</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R67" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,48 +7791,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91035</v>
+        <v>91526</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R70" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7873,7 +7870,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7892,45 +7888,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91526</v>
+        <v>91035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R71" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7971,6 +7970,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>88735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,27 +4017,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R33" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,11 +4086,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>88735</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,31 +4123,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4157,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R34" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,6 +4188,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B33" t="n">
-        <v>88735</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,31 +4017,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R33" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,6 +4082,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>88735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,27 +4124,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R34" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,11 +4193,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>92815</v>
+        <v>83003</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R47" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>83003</v>
+        <v>92815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R48" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B57" t="n">
-        <v>91491</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R57" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91491</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R58" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B62" t="n">
-        <v>91526</v>
+        <v>91491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R62" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B63" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R63" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7791,45 +7791,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B70" t="n">
-        <v>91526</v>
+        <v>91035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R70" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7870,6 +7873,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7888,48 +7892,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B71" t="n">
-        <v>91035</v>
+        <v>91526</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R71" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7970,7 +7971,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>128681483</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128676174</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128681478</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>128681476</v>
       </c>
       <c r="B8" t="n">
-        <v>96005</v>
+        <v>96015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128681477</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128681474</v>
       </c>
       <c r="B10" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128681475</v>
       </c>
       <c r="B11" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128675840</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128823598</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>88735</v>
+        <v>88739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>128829860</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,48 +4325,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B36" t="n">
-        <v>92811</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R36" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4398,77 +4403,78 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>92818</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R37" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4500,30 +4506,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92091</v>
+        <v>92098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>128829154</v>
       </c>
       <c r="B50" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91749</v>
+        <v>91756</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>91497</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R57" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B58" t="n">
-        <v>91491</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R58" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96101</v>
+        <v>96111</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91491</v>
+        <v>91533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R62" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91526</v>
+        <v>91497</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R63" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7791,48 +7791,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91035</v>
+        <v>91533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R70" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7873,7 +7870,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7892,45 +7888,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91526</v>
+        <v>91039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R71" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7971,6 +7970,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92158</v>
+        <v>92165</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>128693765</v>
       </c>
       <c r="B74" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B23" t="n">
-        <v>92822</v>
+        <v>4779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,26 +2920,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2947,13 +2953,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R23" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,7 +2988,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2998,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B24" t="n">
-        <v>4779</v>
+        <v>92822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,32 +3036,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R24" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4325,53 +4325,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>92818</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R36" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4403,78 +4398,77 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B37" t="n">
-        <v>92818</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R37" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4506,24 +4500,30 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B39" t="n">
-        <v>96158</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,34 +4638,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R39" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4724,10 +4729,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>96158</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4735,39 +4740,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R40" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>83007</v>
+        <v>92822</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R47" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>92822</v>
+        <v>83007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R48" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>88746</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,27 +4017,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R33" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,11 +4086,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>88739</v>
+        <v>57722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,31 +4123,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4157,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R34" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,6 +4188,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,7 +4328,7 @@
         <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96165</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,39 +4638,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R39" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,10 +4724,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B40" t="n">
-        <v>96158</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4740,34 +4735,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R40" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92098</v>
+        <v>92105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92822</v>
+        <v>92829</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>96158</v>
+        <v>91046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R45" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>91039</v>
+        <v>96165</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R46" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5441,7 +5441,7 @@
         <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>92822</v>
+        <v>92829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91756</v>
+        <v>91763</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96111</v>
+        <v>96118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92165</v>
+        <v>92172</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>128717747</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>91562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>128717859</v>
       </c>
       <c r="B14" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>128717206</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128717695</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>91562</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128737780</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>128735669</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128738613</v>
       </c>
       <c r="B19" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>128735553</v>
       </c>
       <c r="B20" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128735817</v>
       </c>
       <c r="B21" t="n">
-        <v>91551</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128736979</v>
+        <v>128738401</v>
       </c>
       <c r="B23" t="n">
-        <v>4779</v>
+        <v>92831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,32 +2920,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674876</v>
+        <v>674914</v>
       </c>
       <c r="R23" t="n">
-        <v>6565310</v>
+        <v>6565161</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738401</v>
+        <v>128736979</v>
       </c>
       <c r="B24" t="n">
-        <v>92822</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,26 +3030,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674914</v>
+        <v>674876</v>
       </c>
       <c r="R24" t="n">
-        <v>6565161</v>
+        <v>6565310</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3138,7 @@
         <v>128770626</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128764851</v>
       </c>
       <c r="B26" t="n">
-        <v>91988</v>
+        <v>91997</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128764468</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128764913</v>
       </c>
       <c r="B29" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128761569</v>
       </c>
       <c r="B30" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>88746</v>
+        <v>88748</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>128829860</v>
       </c>
       <c r="B35" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92105</v>
+        <v>92107</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>91046</v>
+        <v>96167</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R45" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>96165</v>
+        <v>91048</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R46" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>92829</v>
+        <v>82999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R47" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>82997</v>
+        <v>92831</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R48" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
         <v>128829154</v>
       </c>
       <c r="B50" t="n">
-        <v>58584</v>
+        <v>58586</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91763</v>
+        <v>91765</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B57" t="n">
-        <v>91504</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R57" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R58" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96118</v>
+        <v>96120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B62" t="n">
-        <v>91540</v>
+        <v>91506</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R62" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B63" t="n">
-        <v>91504</v>
+        <v>91542</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R63" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7791,45 +7791,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>91048</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R70" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7870,6 +7873,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7888,48 +7892,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B71" t="n">
-        <v>91046</v>
+        <v>91542</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R71" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7970,7 +7971,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92172</v>
+        <v>92174</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>128693765</v>
       </c>
       <c r="B74" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B33" t="n">
-        <v>88748</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,31 +4017,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R33" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,6 +4082,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>88748</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,27 +4124,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R34" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,11 +4193,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B39" t="n">
-        <v>96167</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,34 +4638,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R39" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4724,10 +4729,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>96167</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4735,39 +4740,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R40" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>82999</v>
+        <v>92831</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R47" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>92831</v>
+        <v>82999</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R48" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>91506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R57" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B58" t="n">
-        <v>91506</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R58" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91506</v>
+        <v>91542</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R62" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91542</v>
+        <v>91506</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R63" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B66" t="n">
-        <v>91506</v>
+        <v>92871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R66" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B67" t="n">
-        <v>92871</v>
+        <v>91506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R67" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>88748</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,27 +4017,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R33" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,11 +4086,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>88748</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,31 +4123,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4157,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R34" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,6 +4188,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128822674</v>
+        <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,39 +4638,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674928</v>
+        <v>674984</v>
       </c>
       <c r="R39" t="n">
-        <v>6565117</v>
+        <v>6564992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,10 +4724,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128823407</v>
+        <v>128822674</v>
       </c>
       <c r="B40" t="n">
-        <v>96167</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4740,34 +4735,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674984</v>
+        <v>674928</v>
       </c>
       <c r="R40" t="n">
-        <v>6564992</v>
+        <v>6565117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>92831</v>
+        <v>82999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R47" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>82999</v>
+        <v>92831</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R48" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>88748</v>
+        <v>88749</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4325,48 +4325,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B36" t="n">
-        <v>92827</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R36" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4398,77 +4403,78 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>92813</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R37" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4500,30 +4506,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92107</v>
+        <v>92122</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92831</v>
+        <v>92817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>92831</v>
+        <v>92817</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>128826512</v>
       </c>
       <c r="B51" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91765</v>
+        <v>91774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6705,49 +6705,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128896496</v>
+        <v>128896442</v>
       </c>
       <c r="B59" t="n">
-        <v>96120</v>
+        <v>96950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674983</v>
+        <v>674963</v>
       </c>
       <c r="R59" t="n">
-        <v>6565095</v>
+        <v>6565065</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6788,7 +6784,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6807,45 +6802,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128896442</v>
+        <v>128896496</v>
       </c>
       <c r="B60" t="n">
-        <v>96924</v>
+        <v>96146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674963</v>
+        <v>674983</v>
       </c>
       <c r="R60" t="n">
-        <v>6565065</v>
+        <v>6565095</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6886,6 +6885,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B62" t="n">
-        <v>91542</v>
+        <v>91504</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R62" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B63" t="n">
-        <v>91506</v>
+        <v>91540</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R63" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918619</v>
+        <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>92871</v>
+        <v>91504</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674873</v>
+        <v>674863</v>
       </c>
       <c r="R66" t="n">
-        <v>6565272</v>
+        <v>6565199</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918595</v>
+        <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>91506</v>
+        <v>92857</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,21 +7507,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674863</v>
+        <v>674873</v>
       </c>
       <c r="R67" t="n">
-        <v>6565199</v>
+        <v>6565272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7791,48 +7791,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B70" t="n">
-        <v>91048</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R70" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7873,7 +7870,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7892,45 +7888,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B71" t="n">
-        <v>91542</v>
+        <v>91049</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R71" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7971,6 +7970,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92174</v>
+        <v>92189</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -3903,7 +3903,7 @@
         <v>128804078</v>
       </c>
       <c r="B32" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B33" t="n">
-        <v>88749</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,31 +4017,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4050,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R33" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,6 +4082,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>88749</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,27 +4124,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R34" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,11 +4193,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,53 +4325,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128829258</v>
+        <v>128822764</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>92814</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674968</v>
+        <v>674928</v>
       </c>
       <c r="R36" t="n">
-        <v>6564967</v>
+        <v>6565117</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4403,78 +4398,77 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128822764</v>
+        <v>128829258</v>
       </c>
       <c r="B37" t="n">
-        <v>92813</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674928</v>
+        <v>674968</v>
       </c>
       <c r="R37" t="n">
-        <v>6565117</v>
+        <v>6564967</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4506,24 +4500,30 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
         <v>128823232</v>
       </c>
       <c r="B38" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>128826779</v>
       </c>
       <c r="B41" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>128824197</v>
       </c>
       <c r="B42" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>128826613</v>
       </c>
       <c r="B43" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B45" t="n">
-        <v>96193</v>
+        <v>91049</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R45" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B46" t="n">
-        <v>91049</v>
+        <v>96194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R46" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B47" t="n">
-        <v>82999</v>
+        <v>92818</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R47" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B48" t="n">
-        <v>92817</v>
+        <v>82999</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R48" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6705,45 +6705,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128896442</v>
+        <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96950</v>
+        <v>96147</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674963</v>
+        <v>674983</v>
       </c>
       <c r="R59" t="n">
-        <v>6565065</v>
+        <v>6565095</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6784,6 +6788,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6802,49 +6807,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128896496</v>
+        <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96146</v>
+        <v>96951</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674983</v>
+        <v>674963</v>
       </c>
       <c r="R60" t="n">
-        <v>6565095</v>
+        <v>6565065</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6885,7 +6886,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R62" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R63" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128823598</v>
+        <v>128822567</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>88749</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,27 +4017,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>805</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674964</v>
+        <v>674862</v>
       </c>
       <c r="R33" t="n">
-        <v>6564964</v>
+        <v>6565255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,11 +4086,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128822567</v>
+        <v>128823598</v>
       </c>
       <c r="B34" t="n">
-        <v>88749</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,31 +4123,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>805</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4157,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674862</v>
+        <v>674964</v>
       </c>
       <c r="R34" t="n">
-        <v>6565255</v>
+        <v>6564964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,6 +4188,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4630,7 +4630,7 @@
         <v>128823407</v>
       </c>
       <c r="B39" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128825464</v>
+        <v>128826037</v>
       </c>
       <c r="B45" t="n">
-        <v>91049</v>
+        <v>96195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5741</v>
+        <v>2170</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>675052</v>
+        <v>674880</v>
       </c>
       <c r="R45" t="n">
-        <v>6564838</v>
+        <v>6564888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128826037</v>
+        <v>128825464</v>
       </c>
       <c r="B46" t="n">
-        <v>96194</v>
+        <v>91049</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674880</v>
+        <v>675052</v>
       </c>
       <c r="R46" t="n">
-        <v>6564888</v>
+        <v>6564838</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825353</v>
+        <v>128825694</v>
       </c>
       <c r="B47" t="n">
-        <v>92818</v>
+        <v>82999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4363</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675052</v>
+        <v>675051</v>
       </c>
       <c r="R47" t="n">
-        <v>6564838</v>
+        <v>6564828</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825694</v>
+        <v>128825353</v>
       </c>
       <c r="B48" t="n">
-        <v>82999</v>
+        <v>92818</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4363</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675051</v>
+        <v>675052</v>
       </c>
       <c r="R48" t="n">
-        <v>6564828</v>
+        <v>6564838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -6058,7 +6058,7 @@
         <v>128736831</v>
       </c>
       <c r="B53" t="n">
-        <v>91775</v>
+        <v>91778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>128894849</v>
       </c>
       <c r="B57" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91049</v>
+        <v>91052</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7791,45 +7791,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918599</v>
+        <v>128918608</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>91052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674811</v>
+        <v>674660</v>
       </c>
       <c r="R70" t="n">
-        <v>6565023</v>
+        <v>6564999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7870,6 +7873,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7888,48 +7892,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918608</v>
+        <v>128918599</v>
       </c>
       <c r="B71" t="n">
-        <v>91049</v>
+        <v>91543</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674660</v>
+        <v>674811</v>
       </c>
       <c r="R71" t="n">
-        <v>6564999</v>
+        <v>6565023</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7970,7 +7971,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92190</v>
+        <v>92193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -6169,7 +6169,7 @@
         <v>128895248</v>
       </c>
       <c r="B54" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>128897084</v>
       </c>
       <c r="B55" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>128896962</v>
       </c>
       <c r="B56" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128894849</v>
+        <v>128895773</v>
       </c>
       <c r="B57" t="n">
-        <v>91507</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6502,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674836</v>
+        <v>674782</v>
       </c>
       <c r="R57" t="n">
-        <v>6565193</v>
+        <v>6565036</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128895773</v>
+        <v>128894849</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91509</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674782</v>
+        <v>674836</v>
       </c>
       <c r="R58" t="n">
-        <v>6565036</v>
+        <v>6565193</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6708,7 +6708,7 @@
         <v>128896496</v>
       </c>
       <c r="B59" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>128896442</v>
       </c>
       <c r="B60" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>128895670</v>
       </c>
       <c r="B61" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B62" t="n">
-        <v>91543</v>
+        <v>91509</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R62" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B63" t="n">
-        <v>91507</v>
+        <v>91545</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R63" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91052</v>
+        <v>91054</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>128918608</v>
       </c>
       <c r="B70" t="n">
-        <v>91052</v>
+        <v>91054</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>128918599</v>
       </c>
       <c r="B71" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92193</v>
+        <v>92195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -7011,32 +7011,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918596</v>
+        <v>128918598</v>
       </c>
       <c r="B62" t="n">
-        <v>91509</v>
+        <v>91549</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674844</v>
+        <v>674848</v>
       </c>
       <c r="R62" t="n">
-        <v>6565194</v>
+        <v>6565258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,32 +7108,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918598</v>
+        <v>128918596</v>
       </c>
       <c r="B63" t="n">
-        <v>91545</v>
+        <v>91513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674848</v>
+        <v>674844</v>
       </c>
       <c r="R63" t="n">
-        <v>6565258</v>
+        <v>6565194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>128918620</v>
       </c>
       <c r="B64" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>128918593</v>
       </c>
       <c r="B65" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>128918595</v>
       </c>
       <c r="B66" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>128918619</v>
       </c>
       <c r="B67" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>128918607</v>
       </c>
       <c r="B68" t="n">
-        <v>91054</v>
+        <v>91058</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>128918597</v>
       </c>
       <c r="B69" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>128918608</v>
       </c>
       <c r="B70" t="n">
-        <v>91054</v>
+        <v>91058</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>128918599</v>
       </c>
       <c r="B71" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>128918594</v>
       </c>
       <c r="B72" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>128918621</v>
       </c>
       <c r="B73" t="n">
-        <v>92195</v>
+        <v>92199</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111681578</v>
+        <v>128895248</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675002</v>
+        <v>674836</v>
       </c>
       <c r="R2" t="n">
-        <v>6565099</v>
+        <v>6565193</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111682099</v>
+        <v>128896442</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,38 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674987</v>
+        <v>674963</v>
       </c>
       <c r="R3" t="n">
-        <v>6564839</v>
+        <v>6565065</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,57 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128681484</v>
+        <v>128918593</v>
       </c>
       <c r="B4" t="n">
-        <v>8439</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675052</v>
+        <v>674984</v>
       </c>
       <c r="R4" t="n">
-        <v>6564763</v>
+        <v>6565057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128681483</v>
+        <v>128896496</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,40 +987,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674788</v>
+        <v>674983</v>
       </c>
       <c r="R5" t="n">
-        <v>6565036</v>
+        <v>6565095</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,12 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,22 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128676174</v>
+        <v>128825694</v>
       </c>
       <c r="B6" t="n">
-        <v>92864</v>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,44 +1089,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>674599</v>
+        <v>675051</v>
       </c>
       <c r="R6" t="n">
-        <v>6564750</v>
+        <v>6564828</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,48 +1143,42 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tre fruktkroppar intill en tall.</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128681478</v>
+        <v>128822567</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>89104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,34 +1186,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>805</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675053</v>
+        <v>674862</v>
       </c>
       <c r="R7" t="n">
-        <v>6565013</v>
+        <v>6565255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,60 +1269,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128681476</v>
+        <v>128736831</v>
       </c>
       <c r="B8" t="n">
-        <v>96015</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>1100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675141</v>
+        <v>674864</v>
       </c>
       <c r="R8" t="n">
-        <v>6564732</v>
+        <v>6565314</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1371,12 +1349,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,28 +1373,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128681477</v>
+        <v>128735553</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,37 +1403,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675006</v>
+        <v>674855</v>
       </c>
       <c r="R9" t="n">
-        <v>6564847</v>
+        <v>6565248</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1468,12 +1464,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,60 +1494,63 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128681474</v>
+        <v>128764468</v>
       </c>
       <c r="B10" t="n">
-        <v>91039</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675098</v>
+        <v>674810</v>
       </c>
       <c r="R10" t="n">
-        <v>6564749</v>
+        <v>6565023</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1565,12 +1574,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,57 +1604,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128681475</v>
+        <v>128918598</v>
       </c>
       <c r="B11" t="n">
-        <v>91039</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barrskog NV Kvarntorp, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675140</v>
+        <v>674848</v>
       </c>
       <c r="R11" t="n">
-        <v>6564734</v>
+        <v>6565258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,12 +1681,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,65 +1701,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128675840</v>
+        <v>128918599</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674679</v>
+        <v>674811</v>
       </c>
       <c r="R12" t="n">
-        <v>6564816</v>
+        <v>6565023</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,17 +1778,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett flertal exemplar.</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1783,29 +1792,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128717747</v>
+        <v>128764851</v>
       </c>
       <c r="B13" t="n">
-        <v>91562</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,40 +1821,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674816</v>
+        <v>674807</v>
       </c>
       <c r="R13" t="n">
-        <v>6565145</v>
+        <v>6565024</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1870,17 +1882,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En fruktkropp.</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,67 +1906,63 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128717859</v>
+        <v>128918621</v>
       </c>
       <c r="B14" t="n">
-        <v>92873</v>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674621</v>
+        <v>674957</v>
       </c>
       <c r="R14" t="n">
-        <v>6565026</v>
+        <v>6564925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,17 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar.</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1995,29 +2003,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128717206</v>
+        <v>128918597</v>
       </c>
       <c r="B15" t="n">
-        <v>91562</v>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,37 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674650</v>
+        <v>674823</v>
       </c>
       <c r="R15" t="n">
-        <v>6564961</v>
+        <v>6565098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,17 +2086,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,67 +2100,63 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128717695</v>
+        <v>128823407</v>
       </c>
       <c r="B16" t="n">
-        <v>91562</v>
+        <v>96601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674822</v>
+        <v>674984</v>
       </c>
       <c r="R16" t="n">
-        <v>6565133</v>
+        <v>6564992</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,17 +2183,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En fruktkropp</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2207,74 +2197,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128737780</v>
+        <v>128826037</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>96601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674971</v>
+        <v>674880</v>
       </c>
       <c r="R17" t="n">
-        <v>6565154</v>
+        <v>6564888</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2298,22 +2280,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2328,22 +2300,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128735669</v>
+        <v>128681476</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>96458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,40 +2323,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Barrskog NV Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674862</v>
+        <v>675141</v>
       </c>
       <c r="R18" t="n">
-        <v>6565270</v>
+        <v>6564732</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2408,22 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738613</v>
+        <v>128823232</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,44 +2420,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674872</v>
+        <v>674943</v>
       </c>
       <c r="R19" t="n">
-        <v>6565202</v>
+        <v>6564963</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,22 +2474,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:28</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:28</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2552,67 +2494,63 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128735553</v>
+        <v>128826779</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>92497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>3884</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674855</v>
+        <v>674828</v>
       </c>
       <c r="R20" t="n">
-        <v>6565248</v>
+        <v>6565119</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,22 +2574,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2660,8 +2588,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2678,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735817</v>
+        <v>111682099</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,44 +2633,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674894</v>
+        <v>674987</v>
       </c>
       <c r="R21" t="n">
-        <v>6565319</v>
+        <v>6564839</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2750,22 +2688,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,69 +2718,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738796</v>
+        <v>128681477</v>
       </c>
       <c r="B22" t="n">
-        <v>4773</v>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Barrskog NV Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674880</v>
+        <v>675006</v>
       </c>
       <c r="R22" t="n">
-        <v>6565242</v>
+        <v>6564847</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2866,22 +2795,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,67 +2809,63 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738401</v>
+        <v>128822764</v>
       </c>
       <c r="B23" t="n">
-        <v>92831</v>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674914</v>
+        <v>674928</v>
       </c>
       <c r="R23" t="n">
-        <v>6565161</v>
+        <v>6565117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,22 +2892,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,69 +2912,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128736979</v>
+        <v>128897084</v>
       </c>
       <c r="B24" t="n">
-        <v>4779</v>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674876</v>
+        <v>675050</v>
       </c>
       <c r="R24" t="n">
-        <v>6565310</v>
+        <v>6565124</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3093,22 +2989,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,57 +3019,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Hanna Rönnols</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Hanna Rönnols</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128770626</v>
+        <v>128738401</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>93193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674960</v>
+        <v>674914</v>
       </c>
       <c r="R25" t="n">
-        <v>6564975</v>
+        <v>6565161</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,12 +3099,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,67 +3129,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128764851</v>
+        <v>128824197</v>
       </c>
       <c r="B26" t="n">
-        <v>91997</v>
+        <v>93193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>4363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674807</v>
+        <v>675083</v>
       </c>
       <c r="R26" t="n">
-        <v>6565024</v>
+        <v>6564885</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3304,22 +3206,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:39</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:39</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3334,22 +3226,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128761517</v>
+        <v>128825353</v>
       </c>
       <c r="B27" t="n">
-        <v>8439</v>
+        <v>93193</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3357,46 +3249,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>4363</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674829</v>
+        <v>675052</v>
       </c>
       <c r="R27" t="n">
-        <v>6565135</v>
+        <v>6564838</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3420,22 +3303,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:58</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:58</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,63 +3323,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128764468</v>
+        <v>128898290</v>
       </c>
       <c r="B28" t="n">
-        <v>91542</v>
+        <v>93193</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>4363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674810</v>
+        <v>675055</v>
       </c>
       <c r="R28" t="n">
-        <v>6565023</v>
+        <v>6565119</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3530,22 +3400,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,22 +3420,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128764913</v>
+        <v>128918592</v>
       </c>
       <c r="B29" t="n">
-        <v>92871</v>
+        <v>93193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3583,40 +3443,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674797</v>
+        <v>675069</v>
       </c>
       <c r="R29" t="n">
-        <v>6565018</v>
+        <v>6565112</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3640,22 +3497,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3670,22 +3517,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128761569</v>
+        <v>128896962</v>
       </c>
       <c r="B30" t="n">
-        <v>92873</v>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,21 +3540,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3716,17 +3563,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674813</v>
+        <v>675023</v>
       </c>
       <c r="R30" t="n">
-        <v>6565121</v>
+        <v>6565128</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3750,22 +3597,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3774,57 +3621,60 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128804347</v>
+        <v>128694236</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>91930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3832,13 +3682,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674637</v>
+        <v>674760</v>
       </c>
       <c r="R31" t="n">
-        <v>6564804</v>
+        <v>6564953</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3862,17 +3712,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gnagspår på en gran.</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128804078</v>
+        <v>128695020</v>
       </c>
       <c r="B32" t="n">
-        <v>92860</v>
+        <v>91930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3911,24 +3756,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -3938,13 +3787,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674640</v>
+        <v>674673</v>
       </c>
       <c r="R32" t="n">
-        <v>6565050</v>
+        <v>6564961</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3968,17 +3817,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ett flertal fruktkroppar.</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,10 +3850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128822567</v>
+        <v>128717206</v>
       </c>
       <c r="B33" t="n">
-        <v>88749</v>
+        <v>91930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,43 +3861,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>805</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674862</v>
+        <v>674650</v>
       </c>
       <c r="R33" t="n">
-        <v>6565255</v>
+        <v>6564961</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,12 +3918,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,28 +3937,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128823598</v>
+        <v>128717695</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>91930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,39 +3967,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674964</v>
+        <v>674822</v>
       </c>
       <c r="R34" t="n">
-        <v>6564964</v>
+        <v>6565133</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,17 +4024,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hackmärken i död gran.</t>
+          <t>En fruktkropp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4201,28 +4043,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128829860</v>
+        <v>128717747</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>91930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4230,27 +4073,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4258,13 +4100,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>675057</v>
+        <v>674816</v>
       </c>
       <c r="R35" t="n">
-        <v>6564832</v>
+        <v>6565145</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4288,17 +4130,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hackmärken på en tall.</t>
+          <t>En fruktkropp.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,6 +4149,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4325,45 +4168,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128822764</v>
+        <v>128894849</v>
       </c>
       <c r="B36" t="n">
-        <v>92814</v>
+        <v>91872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674928</v>
+        <v>674836</v>
       </c>
       <c r="R36" t="n">
-        <v>6565117</v>
+        <v>6565193</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,12 +4233,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,22 +4263,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128829258</v>
+        <v>128895670</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4433,42 +4286,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674968</v>
+        <v>674812</v>
       </c>
       <c r="R37" t="n">
-        <v>6564967</v>
+        <v>6565025</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4492,17 +4340,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4511,29 +4364,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Hanna Rönnols</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Hanna Rönnols</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128823232</v>
+        <v>128918594</v>
       </c>
       <c r="B38" t="n">
-        <v>92258</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4541,34 +4393,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674943</v>
+        <v>675018</v>
       </c>
       <c r="R38" t="n">
-        <v>6564963</v>
+        <v>6564970</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,12 +4447,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4615,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128823407</v>
+        <v>128918595</v>
       </c>
       <c r="B39" t="n">
-        <v>96195</v>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4638,34 +4490,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674984</v>
+        <v>674863</v>
       </c>
       <c r="R39" t="n">
-        <v>6564992</v>
+        <v>6565199</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,12 +4544,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4712,22 +4564,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128822674</v>
+        <v>128918596</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4735,39 +4587,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674928</v>
+        <v>674844</v>
       </c>
       <c r="R40" t="n">
-        <v>6565117</v>
+        <v>6565194</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,12 +4641,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4814,63 +4661,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128826779</v>
+        <v>128681474</v>
       </c>
       <c r="B41" t="n">
-        <v>92123</v>
+        <v>91409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3884</v>
+        <v>5741</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Barrskog NV Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674828</v>
+        <v>675098</v>
       </c>
       <c r="R41" t="n">
-        <v>6565119</v>
+        <v>6564749</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4894,12 +4738,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4908,79 +4752,63 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>ekar</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Quercus</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128824197</v>
+        <v>128681475</v>
       </c>
       <c r="B42" t="n">
-        <v>92818</v>
+        <v>91409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4363</v>
+        <v>5741</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Barrskog NV Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>675083</v>
+        <v>675140</v>
       </c>
       <c r="R42" t="n">
-        <v>6564885</v>
+        <v>6564734</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,12 +4835,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,22 +4855,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826613</v>
+        <v>128825464</v>
       </c>
       <c r="B43" t="n">
-        <v>92860</v>
+        <v>91409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,21 +4878,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5074,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674674</v>
+        <v>675052</v>
       </c>
       <c r="R43" t="n">
-        <v>6565110</v>
+        <v>6564838</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5136,53 +4964,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128829636</v>
+        <v>128826512</v>
       </c>
       <c r="B44" t="n">
-        <v>5197</v>
+        <v>91409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>5741</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674968</v>
+        <v>674674</v>
       </c>
       <c r="R44" t="n">
-        <v>6564967</v>
+        <v>6565110</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5214,75 +5046,72 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128826037</v>
+        <v>128918606</v>
       </c>
       <c r="B45" t="n">
-        <v>96195</v>
+        <v>91409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2170</v>
+        <v>5741</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674880</v>
+        <v>675155</v>
       </c>
       <c r="R45" t="n">
-        <v>6564888</v>
+        <v>6564854</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5309,46 +5138,47 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128825464</v>
+        <v>128918607</v>
       </c>
       <c r="B46" t="n">
-        <v>91049</v>
+        <v>91409</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5370,16 +5200,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675052</v>
+        <v>674610</v>
       </c>
       <c r="R46" t="n">
-        <v>6564838</v>
+        <v>6564952</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5406,42 +5239,43 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128825694</v>
+        <v>128918608</v>
       </c>
       <c r="B47" t="n">
-        <v>82999</v>
+        <v>91409</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5449,34 +5283,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>5741</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675051</v>
+        <v>674660</v>
       </c>
       <c r="R47" t="n">
-        <v>6564828</v>
+        <v>6564999</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5503,12 +5340,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5517,63 +5354,65 @@
       <c r="AE47" t="b">
         <v>1</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128825353</v>
+        <v>111681578</v>
       </c>
       <c r="B48" t="n">
-        <v>92818</v>
+        <v>93233</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675052</v>
+        <v>675002</v>
       </c>
       <c r="R48" t="n">
-        <v>6564838</v>
+        <v>6565100</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5600,12 +5439,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5620,62 +5469,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128822614</v>
+        <v>128681483</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>93233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Barrskog NV Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674862</v>
+        <v>674788</v>
       </c>
       <c r="R49" t="n">
-        <v>6565255</v>
+        <v>6565036</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5702,12 +5549,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5716,75 +5563,70 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128829154</v>
+        <v>128735669</v>
       </c>
       <c r="B50" t="n">
-        <v>58586</v>
+        <v>93233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>208249</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674959</v>
+        <v>674862</v>
       </c>
       <c r="R50" t="n">
-        <v>6565013</v>
+        <v>6565270</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5808,12 +5650,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5822,76 +5674,73 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128826512</v>
+        <v>128738613</v>
       </c>
       <c r="B51" t="n">
-        <v>91049</v>
+        <v>93233</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674674</v>
+        <v>674872</v>
       </c>
       <c r="R51" t="n">
-        <v>6565110</v>
+        <v>6565202</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5915,12 +5764,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5935,65 +5794,63 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128829056</v>
+        <v>128764913</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>93233</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674959</v>
+        <v>674797</v>
       </c>
       <c r="R52" t="n">
-        <v>6565131</v>
+        <v>6565018</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6017,17 +5874,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gnagspår på gran.</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6036,70 +5898,66 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128736831</v>
+        <v>128918619</v>
       </c>
       <c r="B53" t="n">
-        <v>91778</v>
+        <v>93233</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1100</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674864</v>
+        <v>674873</v>
       </c>
       <c r="R53" t="n">
-        <v>6565314</v>
+        <v>6565272</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6123,22 +5981,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6147,29 +5995,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128895248</v>
+        <v>128918620</v>
       </c>
       <c r="B54" t="n">
-        <v>96958</v>
+        <v>93233</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,37 +6024,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674836</v>
+        <v>675101</v>
       </c>
       <c r="R54" t="n">
-        <v>6565193</v>
+        <v>6564829</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6234,19 +6081,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6261,22 +6098,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128897084</v>
+        <v>128676174</v>
       </c>
       <c r="B55" t="n">
-        <v>92819</v>
+        <v>93235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6284,37 +6121,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>675050</v>
+        <v>674599</v>
       </c>
       <c r="R55" t="n">
-        <v>6565124</v>
+        <v>6564750</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6338,22 +6182,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar intill en tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,69 +6201,67 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hanna Rönnols</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Hanna Rönnols</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128896962</v>
+        <v>128681478</v>
       </c>
       <c r="B56" t="n">
-        <v>92839</v>
+        <v>93235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Barrskog NV Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>675023</v>
+        <v>675053</v>
       </c>
       <c r="R56" t="n">
-        <v>6565128</v>
+        <v>6565013</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,22 +6285,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6472,67 +6299,73 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128895773</v>
+        <v>128694116</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674782</v>
+        <v>674841</v>
       </c>
       <c r="R57" t="n">
-        <v>6565036</v>
+        <v>6564821</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6556,22 +6389,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6580,66 +6403,74 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128894849</v>
+        <v>128694627</v>
       </c>
       <c r="B58" t="n">
-        <v>91509</v>
+        <v>93235</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674836</v>
+        <v>674760</v>
       </c>
       <c r="R58" t="n">
-        <v>6565193</v>
+        <v>6564953</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6663,22 +6494,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6687,70 +6513,70 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128896496</v>
+        <v>128717859</v>
       </c>
       <c r="B59" t="n">
-        <v>96154</v>
+        <v>93235</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674983</v>
+        <v>674621</v>
       </c>
       <c r="R59" t="n">
-        <v>6565095</v>
+        <v>6565026</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6774,12 +6600,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6795,22 +6626,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128896442</v>
+        <v>128737780</v>
       </c>
       <c r="B60" t="n">
-        <v>96958</v>
+        <v>93235</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6818,37 +6649,44 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skansberget, Skansberget, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674963</v>
+        <v>674971</v>
       </c>
       <c r="R60" t="n">
-        <v>6565065</v>
+        <v>6565154</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6872,12 +6710,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6892,60 +6740,63 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128895670</v>
+        <v>128761569</v>
       </c>
       <c r="B61" t="n">
-        <v>91509</v>
+        <v>93235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674812</v>
+        <v>674813</v>
       </c>
       <c r="R61" t="n">
-        <v>6565025</v>
+        <v>6565121</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6969,22 +6820,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6999,22 +6850,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hanna Rönnols</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Hanna Rönnols</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128918598</v>
+        <v>128804078</v>
       </c>
       <c r="B62" t="n">
-        <v>91549</v>
+        <v>93235</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7022,37 +6873,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674848</v>
+        <v>674640</v>
       </c>
       <c r="R62" t="n">
-        <v>6565258</v>
+        <v>6565050</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7076,12 +6930,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ett flertal fruktkroppar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7090,63 +6949,64 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128918596</v>
+        <v>128826613</v>
       </c>
       <c r="B63" t="n">
-        <v>91513</v>
+        <v>93235</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674844</v>
+        <v>674674</v>
       </c>
       <c r="R63" t="n">
-        <v>6565194</v>
+        <v>6565110</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7173,12 +7033,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7193,44 +7053,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128918620</v>
+        <v>128918614</v>
       </c>
       <c r="B64" t="n">
-        <v>92867</v>
+        <v>93235</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7240,10 +7100,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>675101</v>
+        <v>674695</v>
       </c>
       <c r="R64" t="n">
-        <v>6564829</v>
+        <v>6564985</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7302,45 +7162,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128918593</v>
+        <v>128823598</v>
       </c>
       <c r="B65" t="n">
-        <v>96962</v>
+        <v>57950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674984</v>
+        <v>674964</v>
       </c>
       <c r="R65" t="n">
-        <v>6565057</v>
+        <v>6564964</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7367,12 +7232,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7387,22 +7257,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128918595</v>
+        <v>128829860</v>
       </c>
       <c r="B66" t="n">
-        <v>91513</v>
+        <v>57950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,37 +7280,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674863</v>
+        <v>675057</v>
       </c>
       <c r="R66" t="n">
-        <v>6565199</v>
+        <v>6564832</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7464,12 +7338,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Hackmärken på en tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7484,22 +7363,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128918619</v>
+        <v>128738796</v>
       </c>
       <c r="B67" t="n">
-        <v>92867</v>
+        <v>4775</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7507,37 +7386,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>100299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674873</v>
+        <v>674880</v>
       </c>
       <c r="R67" t="n">
-        <v>6565272</v>
+        <v>6565242</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7561,12 +7449,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7575,28 +7473,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128918607</v>
+        <v>128804347</v>
       </c>
       <c r="B68" t="n">
-        <v>91058</v>
+        <v>5179</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7604,26 +7503,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5741</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7631,13 +7532,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>674610</v>
+        <v>674637</v>
       </c>
       <c r="R68" t="n">
-        <v>6564952</v>
+        <v>6564804</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7661,19 +7562,24 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gnagspår på en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
@@ -7682,57 +7588,62 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128918597</v>
+        <v>128822614</v>
       </c>
       <c r="B69" t="n">
-        <v>90581</v>
+        <v>5179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>674823</v>
+        <v>674862</v>
       </c>
       <c r="R69" t="n">
-        <v>6565098</v>
+        <v>6565255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,12 +7670,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7779,22 +7690,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128918608</v>
+        <v>128829056</v>
       </c>
       <c r="B70" t="n">
-        <v>91058</v>
+        <v>5179</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7802,26 +7713,28 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7829,13 +7742,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674660</v>
+        <v>674959</v>
       </c>
       <c r="R70" t="n">
-        <v>6564999</v>
+        <v>6565131</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7859,19 +7772,24 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
@@ -7880,60 +7798,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128918599</v>
+        <v>128829258</v>
       </c>
       <c r="B71" t="n">
-        <v>91549</v>
+        <v>5179</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vidja, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674811</v>
+        <v>674968</v>
       </c>
       <c r="R71" t="n">
-        <v>6565023</v>
+        <v>6564967</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7957,12 +7880,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av vågbandad barkbock.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7971,28 +7899,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128918594</v>
+        <v>128736979</v>
       </c>
       <c r="B72" t="n">
-        <v>91513</v>
+        <v>4781</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,37 +7929,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>675018</v>
+        <v>674876</v>
       </c>
       <c r="R72" t="n">
-        <v>6564970</v>
+        <v>6565310</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8054,12 +7992,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8074,22 +8022,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128918621</v>
+        <v>128822674</v>
       </c>
       <c r="B73" t="n">
-        <v>92199</v>
+        <v>4781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8097,34 +8045,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vidja, Srm</t>
+          <t>Skansberget, Skansberget, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>674957</v>
+        <v>674928</v>
       </c>
       <c r="R73" t="n">
-        <v>6564925</v>
+        <v>6565117</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8151,12 +8104,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8171,12 +8124,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8186,7 +8139,7 @@
         <v>128693765</v>
       </c>
       <c r="B74" t="n">
-        <v>57887</v>
+        <v>58114</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8289,6 +8242,1073 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128829636</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>674968</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6564967</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Gnagspår på gran. På samma träd även gnagspår av bronshjon.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128693627</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>674749</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6564855</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128895773</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skansberget, Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>674782</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6565036</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128681484</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Barrskog NV Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>675052</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6564763</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128761517</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>674829</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6565135</v>
+      </c>
+      <c r="S79" t="n">
+        <v>6</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128694205</v>
+      </c>
+      <c r="B80" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>674834</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6564900</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128829154</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>674959</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6565013</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128734687</v>
+      </c>
+      <c r="B82" t="n">
+        <v>40282</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>214801</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre poppelglasvinge</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Eusphecia melanocephala</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Dalman, 1816</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skansberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>674812</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6565313</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128675840</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>674679</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6564816</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ett flertal exemplar.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128770626</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>674960</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6564975</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40110-2025 artfynd.xlsx
+++ b/artfynd/A 40110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128825694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826037</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681476</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128823232</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111682099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1362,6 +1397,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128824197</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,6 +1601,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128825353</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128694236</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128695020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128717206</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918594</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681474</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681475</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128825464</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918606</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918607</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918620</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676174</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2774,6 +2879,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128694116</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2884,6 +2994,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128694627</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2991,6 +3106,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128823598</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,6 +3217,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128829860</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3205,6 +3330,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804347</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3313,6 +3443,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128829258</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3422,6 +3557,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128693765</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128829636</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3633,6 +3778,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128693627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3730,6 +3880,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681484</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3837,6 +3992,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128694205</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3945,6 +4105,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675840</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4052,6 +4217,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128895248</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4149,6 +4319,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128896442</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4246,6 +4421,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918593</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4348,6 +4528,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128896496</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4454,6 +4639,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822567</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4565,6 +4755,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128736831</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4679,6 +4874,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128735553</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4789,6 +4989,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128764468</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4886,6 +5091,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918598</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4983,6 +5193,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918599</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5097,6 +5312,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128764851</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5194,6 +5414,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918597</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5291,6 +5516,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128823407</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5407,6 +5637,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826779</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5504,6 +5739,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822764</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5611,6 +5851,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128897084</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5721,6 +5966,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738401</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5818,6 +6068,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128898290</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5915,6 +6170,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918592</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6026,6 +6286,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128896962</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6132,6 +6397,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128717695</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6238,6 +6508,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128717747</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6345,6 +6620,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128894849</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6452,6 +6732,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128895670</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6549,6 +6834,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918595</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6646,6 +6936,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918596</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6752,6 +7047,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826512</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6853,6 +7153,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918608</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6961,6 +7266,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111681578</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7062,6 +7372,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681483</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7172,6 +7487,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128735669</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7286,6 +7606,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738613</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7396,6 +7721,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128764913</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7493,6 +7823,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918619</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7590,6 +7925,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681478</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7696,6 +8036,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128717859</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7810,6 +8155,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128737780</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7920,6 +8270,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128761569</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8026,6 +8381,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804078</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8123,6 +8483,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826613</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8220,6 +8585,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918614</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8337,6 +8707,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738796</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8439,6 +8814,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822614</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8547,6 +8927,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128829056</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8663,6 +9048,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128736979</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8765,6 +9155,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822674</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8872,6 +9267,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128895773</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8988,6 +9388,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128761517</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9095,6 +9500,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128829154</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9212,6 +9622,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128734687</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9309,8 +9724,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128770626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>